--- a/VerveStacks_NOR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8324EC1A-13D3-45CF-A0BD-70EADBC007BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4144309-0EC1-4C44-B35B-3BCF96C3C4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,34 +520,34 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>NOR68p0N16p4E_NOR</t>
+  </si>
+  <si>
+    <t>at grid node - NOR68p0N16p4E_NOR</t>
+  </si>
+  <si>
     <t>Narvik_NOR</t>
   </si>
   <si>
     <t>at grid node - Narvik_NOR</t>
   </si>
   <si>
+    <t>Arendal_NOR</t>
+  </si>
+  <si>
+    <t>at grid node - Arendal_NOR</t>
+  </si>
+  <si>
+    <t>Namsos_NOR</t>
+  </si>
+  <si>
+    <t>at grid node - Namsos_NOR</t>
+  </si>
+  <si>
     <t>Bergen_NOR</t>
   </si>
   <si>
     <t>at grid node - Bergen_NOR</t>
-  </si>
-  <si>
-    <t>NOR68p0N16p4E_NOR</t>
-  </si>
-  <si>
-    <t>at grid node - NOR68p0N16p4E_NOR</t>
-  </si>
-  <si>
-    <t>Namsos_NOR</t>
-  </si>
-  <si>
-    <t>at grid node - Namsos_NOR</t>
-  </si>
-  <si>
-    <t>Arendal_NOR</t>
-  </si>
-  <si>
-    <t>at grid node - Arendal_NOR</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1054,10 +1054,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O11" t="s">
         <v>159</v>
@@ -1116,10 +1116,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="O12" t="s">
         <v>159</v>
@@ -1154,10 +1154,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N13" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="O13" t="s">
         <v>159</v>
@@ -1180,10 +1180,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="N14" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="O14" t="s">
         <v>159</v>
@@ -1206,10 +1206,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="N15" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="O15" t="s">
         <v>159</v>
@@ -1232,10 +1232,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="N16" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="O16" t="s">
         <v>159</v>
@@ -1258,10 +1258,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="N17" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="O17" t="s">
         <v>159</v>
@@ -1284,10 +1284,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="N18" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="O18" t="s">
         <v>159</v>
@@ -1310,10 +1310,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="O19" t="s">
         <v>159</v>
@@ -1336,10 +1336,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="N20" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="O20" t="s">
         <v>159</v>
@@ -1362,10 +1362,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="N21" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="O21" t="s">
         <v>159</v>
@@ -1388,10 +1388,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="N22" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="O22" t="s">
         <v>159</v>
@@ -1414,10 +1414,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="N23" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="O23" t="s">
         <v>159</v>
@@ -1466,10 +1466,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="N25" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="O25" t="s">
         <v>159</v>
@@ -1492,10 +1492,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="N26" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="O26" t="s">
         <v>159</v>
@@ -1518,10 +1518,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="N27" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="O27" t="s">
         <v>159</v>
@@ -1544,10 +1544,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="N28" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="O28" t="s">
         <v>159</v>
@@ -1570,10 +1570,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="N29" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="O29" t="s">
         <v>159</v>
@@ -1596,10 +1596,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="N30" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="O30" t="s">
         <v>159</v>
@@ -1622,10 +1622,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="N31" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="O31" t="s">
         <v>159</v>
@@ -1648,10 +1648,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="N32" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="O32" t="s">
         <v>159</v>
@@ -1674,10 +1674,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="N33" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="O33" t="s">
         <v>159</v>
@@ -1700,10 +1700,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N34" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="O34" t="s">
         <v>159</v>
@@ -1726,10 +1726,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="N35" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="O35" t="s">
         <v>159</v>
@@ -1752,10 +1752,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="N36" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="O36" t="s">
         <v>159</v>
@@ -1778,10 +1778,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N37" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="O37" t="s">
         <v>159</v>
@@ -1804,10 +1804,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="N38" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="O38" t="s">
         <v>159</v>
@@ -1830,10 +1830,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="N39" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="O39" t="s">
         <v>159</v>
@@ -1856,10 +1856,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="N40" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="O40" t="s">
         <v>159</v>
@@ -1882,10 +1882,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N41" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O41" t="s">
         <v>159</v>
@@ -1908,10 +1908,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="N42" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="O42" t="s">
         <v>159</v>
@@ -1934,10 +1934,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="N43" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="O43" t="s">
         <v>159</v>
@@ -1960,10 +1960,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="N44" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="O44" t="s">
         <v>159</v>
@@ -1986,10 +1986,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="N45" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="O45" t="s">
         <v>159</v>
@@ -2000,10 +2000,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="N46" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="O46" t="s">
         <v>159</v>
@@ -2014,10 +2014,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="N47" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="O47" t="s">
         <v>159</v>
@@ -2028,10 +2028,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="N48" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="O48" t="s">
         <v>159</v>
